--- a/incident_report_forms/020_oil_spill_incident_form--incident_report_forms.xlsx
+++ b/incident_report_forms/020_oil_spill_incident_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'type_a',_'label':_'type_a',_'value':_'type_a'}</t>
+          <t>type_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'type_a', 'label': 'Type A', 'value': 'type_a'}</t>
+          <t>Type A</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'type_b',_'label':_'type_b',_'value':_'type_b'}</t>
+          <t>type_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'type_b', 'label': 'Type B', 'value': 'type_b'}</t>
+          <t>Type B</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'type_c',_'label':_'type_c',_'value':_'type_c'}</t>
+          <t>type_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'type_c', 'label': 'Type C', 'value': 'type_c'}</t>
+          <t>Type C</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'responder_1',_'label':_'responder_1',_'value':_'responder_1'}</t>
+          <t>responder_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'responder_1', 'label': 'Responder 1', 'value': 'responder_1'}</t>
+          <t>Responder 1</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'responder_2',_'label':_'responder_2',_'value':_'responder_2'}</t>
+          <t>responder_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'responder_2', 'label': 'Responder 2', 'value': 'responder_2'}</t>
+          <t>Responder 2</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'responder_3',_'label':_'responder_3',_'value':_'responder_3'}</t>
+          <t>responder_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'responder_3', 'label': 'Responder 3', 'value': 'responder_3'}</t>
+          <t>Responder 3</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'containment_a',_'label':_'containment_a',_'value':_'containment_a'}</t>
+          <t>containment_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'containment_a', 'label': 'Containment A', 'value': 'containment_a'}</t>
+          <t>Containment A</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'containment_b',_'label':_'containment_b',_'value':_'containment_b'}</t>
+          <t>containment_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'containment_b', 'label': 'Containment B', 'value': 'containment_b'}</t>
+          <t>Containment B</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'containment_c',_'label':_'containment_c',_'value':_'containment_c'}</t>
+          <t>containment_c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'containment_c', 'label': 'Containment C', 'value': 'containment_c'}</t>
+          <t>Containment C</t>
         </is>
       </c>
     </row>
